--- a/光伏配储项目/电价数据/2026/叶塘站.xlsx
+++ b/光伏配储项目/电价数据/2026/叶塘站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.42241</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38452</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.79337</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.4674</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.48888</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.42933</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.43943</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.39018</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.39908</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.38554</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.37504</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.37714</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.36786</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.36345</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.35498</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.36378</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.37183</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.37015</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.33879</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.35855</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.35517</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.37975</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.36126</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.38217</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.37749</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.38561</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.37932</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.39504</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.41149</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.3083</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.3108399999999999</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.31977</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.33169</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.34924</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32241</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.24535</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.12375</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>-0.01568</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.06520000000000001</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.06906999999999999</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.05457</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.29372</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.5159</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.5612</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.74311</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.14706</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39649</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.39318</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43418</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.441</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.66828</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.89386</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.50404</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.21769</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.35203</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.17118</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.04631</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.31378</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.41591</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.45702</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.70936</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.76124</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.13762</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.9528799999999999</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.91267</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.80825</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.77078</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.5201</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.49105</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.47115</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.42138</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.43174</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.73405</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.9105599999999999</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.97645</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.51449</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.54435</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5219199999999999</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.52207</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.50327</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.4084</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.48367</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.3847</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.39404</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.53226</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33906</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.40744</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.39363</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.39336</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.49551</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.4438</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.44521</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.43708</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.52395</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>1.71022</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>1.61292</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>1.57574</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.56301</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.58592</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38594</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.36652</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.39885</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.49447</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.33823</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.25669</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35761</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30807</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29924</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.16847</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>-0.01645</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.39492</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.37689</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.54055</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.17855</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>-0.01156</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>-0.04788000000000001</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.30516</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.32747</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.6066900000000001</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.7746499999999999</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.80844</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.19401</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.43054</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.14546</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.8672300000000001</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.23346</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.1296</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.41931</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.17369</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.1139</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.67226</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.00739</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.9302</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.98553</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.8255399999999999</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.70043</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.45565</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>1.67909</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>1.74272</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.45516</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43319</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44919</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33428</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.38004</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35766</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33553</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.52342</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.5020899999999999</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.50204</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.3742200000000001</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.45351</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.42171</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.37483</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39606</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38972</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36824</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43936</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.45665</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33811</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37594</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.40463</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.37323</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37368</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.3606</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36666</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35616</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.4088</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.38133</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.40344</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.40843</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.48804</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45164</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44917</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34906</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.40111</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35588</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36711</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34831</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.22941</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.32078</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.8033400000000001</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>-0.009859999999999999</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.32962</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.33758</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.44841</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.38858</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.43655</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.36045</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.34889</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.44467</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.34835</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>1.15273</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>1.22595</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.33161</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.63037</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.67043</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.47042</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.50762</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>1.5561</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>1.07515</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.4395</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.51079</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.63178</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.69989</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.71524</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>1.3761</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>1.17527</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>1.41917</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>1.54134</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.43803</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.46228</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.40017</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.3618</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.35026</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34304</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.5250499999999999</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.51146</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.44613</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.39755</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.40048</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.37303</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.3644</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.39682</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.39424</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36914</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.45993</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.36675</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.35366</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.36373</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.36525</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.34127</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33869</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33888</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33429</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35272</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.34158</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35541</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.39285</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39469</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.35403</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.38179</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34716</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39854</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.42224</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.4372200000000001</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.3583</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.41816</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34206</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.35586</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.30756</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.32604</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.60015</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.30242</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.40815</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.31877</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.22155</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.1949</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.32335</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.34874</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.36716</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.3083</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.40985</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.6441699999999999</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.32664</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.30259</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31403</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.3424700000000001</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>1.30355</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>1.1143</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.41228</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.33053</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.45141</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.26936</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.47878</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.5292</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.4511</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.47556</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.40451</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.60753</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>1.39799</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>1.41346</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.60176</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.7243999999999999</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.52637</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.49819</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50444</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.45002</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.42728</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.41866</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.42854</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.35701</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.3746</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34938</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34498</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32131</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31279</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31946</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.32253</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.33239</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.36748</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.34663</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.37962</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35756</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33866</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32657</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32715</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32012</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31867</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31551</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31763</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31892</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31723</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31086</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31223</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31679</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31549</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30907</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.3085</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31321</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31436</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31733</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31671</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.29378</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.30684</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.28654</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.2865</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.30578</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.30049</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30383</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.27191</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.25769</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.0363</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.13326</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.03888</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.02486</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.02698</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.2341</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29636</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29898</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29577</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30256</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.38436</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.67186</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.64383</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.6607000000000001</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.5287200000000001</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.42728</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.68325</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.6097</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.65088</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.62985</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.47867</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.5572699999999999</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.60953</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.90016</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.42472</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.39401</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.35554</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.38594</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.5321</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.37535</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.9358200000000001</v>
+      </c>
+      <c r="E122" t="n">
+        <v>1.54801</v>
+      </c>
+      <c r="F122" t="n">
+        <v>1.3684</v>
+      </c>
+      <c r="G122" t="n">
+        <v>1.47362</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.52744</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.74052</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.51822</v>
+      </c>
+      <c r="K122" t="n">
+        <v>1.09073</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.47805</v>
+      </c>
+      <c r="M122" t="n">
+        <v>1.25734</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.9292</v>
+      </c>
+      <c r="O122" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.50803</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.51315</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.49586</v>
+      </c>
+      <c r="S122" t="n">
+        <v>1.09644</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.76911</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.98139</v>
+      </c>
+      <c r="V122" t="n">
+        <v>1.01823</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.46896</v>
+      </c>
+      <c r="X122" t="n">
+        <v>1.1179</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.49615</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.82001</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.77651</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.51285</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>1.10054</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.57848</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10156</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04282</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04575</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04489</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.29173</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.00557</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.19772</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04504</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.26289</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.14069</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04334</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04548</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04338</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.01175</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04537</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.05186</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05004</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19974</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29281</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29224</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.35531</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.40519</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.4468</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.5124500000000001</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.48418</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.44091</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.48164</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.3341</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31053</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.6399600000000001</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.47285</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32784</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27068</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31624</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29725</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.35334</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38134</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.43054</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.46036</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41842</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41525</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.39801</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.4024</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15655</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29425</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31265</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62203</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78572</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92038</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49455</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9141900000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86286</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29619</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35361</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88746</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63159</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18705</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8697</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.61151</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33081</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03289</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5307500000000001</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79096</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5552699999999999</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77295</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77752</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87385</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49312</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39865</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39985</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44991</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20696</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87882</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55101</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62181</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53831</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43713</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45126</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38816</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42031</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.47931</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.43838</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.42848</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.423</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.56076</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.6240800000000001</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.45144</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.47417</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.47334</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.40844</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.39343</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.46759</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.8733099999999999</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.48861</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.53259</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.59562</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.82031</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>1.29924</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>1.03889</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.8630599999999999</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>1.42819</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.89089</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.47609</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>1.1085</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>1.33777</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.85812</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.97909</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87503</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.43712</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>1.09417</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.41005</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.48355</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.6001799999999999</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.40743</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.45728</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.38881</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32089</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.41433</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.33463</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.32017</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.34224</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.55741</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.30122</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.47591</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.37254</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.35964</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29597</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.33623</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.41524</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.34844</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>1.04429</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.56633</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.59981</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.56645</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.65543</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.5587000000000001</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.51516</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.60251</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.5011</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.499</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.49128</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.5715</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.5625399999999999</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.98881</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>1.00417</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>1.22339</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>1.01781</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.8549</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.83102</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.5143099999999999</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="C125" t="n">
+        <v>1.07638</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.64378</v>
+      </c>
+      <c r="E125" t="n">
+        <v>1.01637</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.94236</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.81933</v>
+      </c>
+      <c r="H125" t="n">
+        <v>1.2151</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.75215</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.93015</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.5937</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.6396499999999999</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.57755</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.54796</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.63037</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.49049</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.64015</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.5848300000000001</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.46637</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.9790800000000001</v>
+      </c>
+      <c r="U125" t="n">
+        <v>1.48677</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.64136</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.87588</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.5918</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.6672400000000001</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.66973</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.6662899999999999</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.50604</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.43057</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.5299400000000001</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.52452</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.51332</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.5774199999999999</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.3769</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.3624</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.30906</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.10955</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.26205</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>-0.03255</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30407</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.31039</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.25762</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.27488</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.15091</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.26319</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26046</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.20383</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.31803</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29898</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.33139</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.29127</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.32086</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.32115</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.37031</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.38384</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.38408</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.48685</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.47686</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.39469</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>1.16904</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.41491</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.5041100000000001</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.31842</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.44411</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.5265599999999999</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.39106</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29621</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.5867</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.26349</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.61812</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.5204099999999999</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.5202599999999999</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.52501</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.28496</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.66918</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.49889</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.5835199999999999</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.47939</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.6183099999999999</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.50757</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.7662100000000001</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.55676</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>1.21239</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.50383</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.5317999999999999</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.43537</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.50741</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.6260800000000001</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.58125</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.8892100000000001</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.5250199999999999</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.91389</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.9392200000000001</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>1.04539</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.16873</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.66229</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.38286</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.89137</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.9850399999999999</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.84134</v>
+      </c>
+      <c r="I126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J126" t="n">
+        <v>1.70107</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.63029</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.6824199999999999</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.61751</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.9274600000000001</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.59304</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.58486</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.8756900000000001</v>
+      </c>
+      <c r="R126" t="n">
+        <v>1.47345</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.58387</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.6079</v>
+      </c>
+      <c r="U126" t="n">
+        <v>1.02884</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.60636</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.55348</v>
+      </c>
+      <c r="X126" t="n">
+        <v>1.17262</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>1.30815</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.5663400000000001</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.59177</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>1.19509</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.58373</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.5741499999999999</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.99007</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>1.17557</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.56889</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>1.0243</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.66583</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.5239299999999999</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>1.3193</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.46779</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.88249</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.69533</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.4352200000000001</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.5449400000000001</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.38147</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.48159</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.40685</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>1.24689</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.5241399999999999</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.2551</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.41455</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.2055</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.3728399999999999</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27726</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.05349</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.4045299999999999</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30382</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26881</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.26498</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.31363</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28749</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.36063</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.36201</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.34344</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.39545</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.37568</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.4464</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.51705</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.42863</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.5861499999999999</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.5754</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.7934500000000001</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.79544</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.4964</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.52824</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.49434</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.6785399999999999</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.5541900000000001</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.51052</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.79874</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.61073</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.53074</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.5165700000000001</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>1.27218</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>1.18985</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>1.2363</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>1.17123</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.73387</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.9358300000000001</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.76571</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.69294</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.5546599999999999</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.72999</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.53986</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.71036</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>1.25247</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.80108</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.86127</v>
+      </c>
+      <c r="F127" t="n">
+        <v>1.30996</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.49561</v>
+      </c>
+      <c r="H127" t="n">
+        <v>1.0806</v>
+      </c>
+      <c r="I127" t="n">
+        <v>1.08658</v>
+      </c>
+      <c r="J127" t="n">
+        <v>1.11746</v>
+      </c>
+      <c r="K127" t="n">
+        <v>1.0729</v>
+      </c>
+      <c r="L127" t="n">
+        <v>1.2538</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.73522</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.7343200000000001</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.7373500000000001</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.48568</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.48168</v>
+      </c>
+      <c r="R127" t="n">
+        <v>1.24481</v>
+      </c>
+      <c r="S127" t="n">
+        <v>1.24416</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.48093</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.49637</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.47705</v>
+      </c>
+      <c r="W127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="X127" t="n">
+        <v>1.07019</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>1.48437</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>1.15653</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>1.52161</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>1.43067</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.80447</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.5049</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.98556</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.66265</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>1.2966</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.48125</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.55674</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>1.18448</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.7095</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.79086</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.80863</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>1.10874</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.5796</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.07468000000000001</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.28654</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.1312</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>-0.01217</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.00578</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.27137</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.02555</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.2031</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>-0.008880000000000001</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.25781</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.36706</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.10704</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>-0.03375</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.2271</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>-0.03417</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.6296</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.49736</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.70725</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.5438200000000001</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.7307</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.66875</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.72722</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.8942</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.58016</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.78904</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.58477</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.8958400000000001</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.72526</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.86702</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>1.28003</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.96299</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.88505</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.97602</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.92498</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>1.24419</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>1.2212</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>1.19273</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>1.21247</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.60414</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.56759</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.55514</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.56037</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.5539500000000001</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.76074</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.7516699999999999</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.87483</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.71049</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.60502</v>
+      </c>
+      <c r="C128" t="n">
+        <v>1.75752</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.54914</v>
+      </c>
+      <c r="E128" t="n">
+        <v>1.31967</v>
+      </c>
+      <c r="F128" t="n">
+        <v>1.04221</v>
+      </c>
+      <c r="G128" t="n">
+        <v>1.00193</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.7545499999999999</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.8119400000000001</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.7970700000000001</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.85993</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.5400700000000001</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.5306799999999999</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.76555</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.65654</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.84199</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.7268</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.8239299999999999</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.6422599999999999</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.6250399999999999</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.65489</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.61102</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.58723</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.6113</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.58723</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.6180099999999999</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>1.25197</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.77211</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.8090000000000001</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.68413</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.55052</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.60654</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.55072</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.50732</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.56002</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.56952</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.5262100000000001</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.38148</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.43963</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31535</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.35359</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.23839</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.25942</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.18801</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.14521</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.46322</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.18275</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.28158</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.21708</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30085</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30082</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31751</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31498</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.28484</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.52951</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31287</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.32728</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.2452</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.46304</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.49899</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.9843999999999999</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.62056</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.54972</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>1.17889</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.5741799999999999</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.69939</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.53798</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.50736</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.63628</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.58724</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.5794400000000001</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.50356</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.49543</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.57212</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.6791699999999999</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>1.33033</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.65346</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.41055</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.7585700000000001</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.4571</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.5986</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.55964</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.6337200000000001</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.62915</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.8862300000000001</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.4929</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.5169199999999999</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.6203</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.64127</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.5794199999999999</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.8783500000000001</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.7637200000000001</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.78699</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.59373</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.6567999999999999</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.45036</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.678</v>
+      </c>
+      <c r="D129" t="n">
+        <v>1.61553</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.53124</v>
+      </c>
+      <c r="F129" t="n">
+        <v>1.59397</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.7523300000000001</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.61475</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.81432</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.72139</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.70223</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.60846</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.63858</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.6050099999999999</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.6196200000000001</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.50748</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.6475700000000001</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.59882</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.59337</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.50371</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.49917</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.5796</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.5004700000000001</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.49579</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.59009</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.5928099999999999</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.6419</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.86885</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.5406</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.75514</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.70585</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.50099</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.5804</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.66195</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.53274</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.60212</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.29676</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.5952200000000001</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.84356</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.53911</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.677</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.64732</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.5320499999999999</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.6049099999999999</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.6432599999999999</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.5207200000000001</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.58682</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.5268200000000001</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.68032</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.26717</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.26775</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.31879</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.5530900000000001</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>1.1638</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.39366</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.76227</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.5468</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.52566</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.5509400000000001</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.53874</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.50204</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.6576799999999999</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.55325</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.46675</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.55088</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.9087799999999999</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.72122</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.52773</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.54135</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.60381</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.50138</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.59982</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.34888</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.48658</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.7667200000000001</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.64023</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.55214</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.6306799999999999</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.61191</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.8809600000000001</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.55001</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.5382</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.67352</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.41798</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.36104</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.5394</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.42229</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.56894</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.68289</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.69494</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>1.08988</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32005</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.77475</v>
+      </c>
+      <c r="D130" t="n">
+        <v>1.19386</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.5700299999999999</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.6983200000000001</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.6345599999999999</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.7178</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.85722</v>
+      </c>
+      <c r="J130" t="n">
+        <v>1.13012</v>
+      </c>
+      <c r="K130" t="n">
+        <v>1.06191</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.69135</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.63013</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.63564</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.62912</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.61176</v>
+      </c>
+      <c r="R130" t="n">
+        <v>1.08021</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.48552</v>
+      </c>
+      <c r="T130" t="n">
+        <v>1.09071</v>
+      </c>
+      <c r="U130" t="n">
+        <v>1.25585</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.78132</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.48074</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.48392</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.67265</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>1.09044</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>1.08895</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>1.05233</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>1.15033</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>1.34216</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>1.28862</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>1.087</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.83736</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.6205700000000001</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.51659</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.5421699999999999</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.54438</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.49688</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.50502</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.82572</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.50854</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.43957</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.50891</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.5774400000000001</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.60568</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.62026</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.6167</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.48046</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.58109</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.44697</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.5758</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.45726</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.52597</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.49109</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.49402</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.4993</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.5941000000000001</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.58172</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.57036</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.61681</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.5557799999999999</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.53338</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>1.07577</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.6584800000000001</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.50845</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.48367</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.8445900000000001</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.73164</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.5948099999999999</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.58008</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.5191399999999999</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.54677</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.60145</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.62295</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>1.28609</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.6210599999999999</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>1.016</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.50937</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.8439</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.52291</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.8596699999999999</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.5241</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.8310299999999999</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.52424</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.9739500000000001</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.9092100000000001</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.53471</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>1.29846</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.51862</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.93235</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.5317000000000001</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>1.18086</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>1.35106</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.5124299999999999</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.97236</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.51203</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.59487</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.5127</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.5117</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.51273</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.51366</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.51315</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.51235</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.7219099999999999</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.5117</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.5085500000000001</v>
+      </c>
+      <c r="L131" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.50934</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.6732100000000001</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.69635</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.6806</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.50188</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.5023500000000001</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.6324500000000001</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.8361499999999999</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.48669</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.6383</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.5018899999999999</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.7064900000000001</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.6150800000000001</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.7006599999999999</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.50735</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.6163</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.6732899999999999</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.67598</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.49863</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.6639700000000001</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.62219</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.69833</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.59858</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.6449</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.61837</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.51616</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.51667</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.48494</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.45304</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.37276</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.41283</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.41294</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.38309</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.45294</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.43845</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32937</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31829</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37048</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.33066</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.53359</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.41719</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.37103</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.41119</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.40357</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.35648</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.37882</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.43915</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.49047</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.5374</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.4321</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.47832</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.56479</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.5185700000000001</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.5537799999999999</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.5196499999999999</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.5219400000000001</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.53208</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.51225</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.5991799999999999</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.51428</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.59435</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.52108</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.52612</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.51103</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.6786</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.79979</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.72419</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.7099800000000001</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.96426</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.5861799999999999</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.69753</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.53811</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.8173899999999999</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>1.06446</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>1.01852</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>1.19584</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.94232</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.51267</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.5168200000000001</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.5214299999999999</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.50186</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.60312</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32191</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.5736</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.53875</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.63174</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.52451</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.52166</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.52132</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.52449</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.5205700000000001</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.6051299999999999</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.52144</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.5153</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.5224500000000001</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.6210800000000001</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.51859</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.51454</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.61987</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.52195</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.52227</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.51001</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.84173</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.52124</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.51898</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.52254</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.52254</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.7606900000000001</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.52835</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.54235</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.51903</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.5189400000000001</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.5136499999999999</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.51434</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.52037</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.5197000000000001</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.44857</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.54406</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.5230900000000001</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.70382</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.25175</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.0429</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.31007</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28071</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.30942</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.01397</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.27397</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.29088</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.29345</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.20937</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.06016</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.15877</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.21857</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.20561</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.27352</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.25277</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.29077</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.42063</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.6247699999999999</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.2638</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29005</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.48941</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.53525</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.5528099999999999</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.6849500000000001</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.5198400000000001</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.56437</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.35585</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.41872</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33368</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.55665</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.5307799999999999</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.8386699999999999</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32094</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>1.143</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.39308</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.13472</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.64183</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.83316</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.79087</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.82148</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>1.67616</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.99737</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>1.52541</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.6774199999999999</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.58941</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.59723</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.05103</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>1.49242</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>1.04395</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.9732499999999999</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.6938</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.53586</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.64059</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.6079600000000001</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34564</v>
+      </c>
+      <c r="C133" t="n">
+        <v>1.3517</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E133" t="n">
+        <v>1.51277</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.9385399999999999</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.94967</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.8504299999999999</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.91777</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.87717</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.94068</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.81953</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.5555399999999999</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.82468</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.8180299999999999</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.7544099999999999</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.54892</v>
+      </c>
+      <c r="S133" t="n">
+        <v>1.00553</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.8128200000000001</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.9958400000000001</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.82836</v>
+      </c>
+      <c r="W133" t="n">
+        <v>1.0097</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.92286</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.9636699999999999</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.96737</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>1.36264</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>1.27219</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>1.53852</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>1.20399</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>1.4955</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>1.18707</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.61566</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.54826</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.57659</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.59521</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.63175</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.64816</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.71296</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.5954400000000001</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.7185</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.52163</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.87361</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.97523</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.82184</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.5842000000000001</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.53152</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.52976</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.31245</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.33603</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.32711</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.4056</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.6567200000000001</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.37683</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.7135</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.27726</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.49561</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.5334800000000001</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.8892899999999999</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.52807</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.45419</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.5099399999999999</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.50775</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.6627799999999999</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.52154</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.9968899999999999</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.94531</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.96809</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.8239299999999999</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>1.01192</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.75149</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>1.08885</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>1.04266</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>1.38398</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>1.19107</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>1.55051</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>1.56869</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.92896</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.78299</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.8332000000000001</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>1.41204</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>1.45636</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>1.37574</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>1.31785</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>1.30173</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.9313899999999999</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1.76356</v>
+      </c>
+      <c r="D134" t="n">
+        <v>1.00468</v>
+      </c>
+      <c r="E134" t="n">
+        <v>1.09466</v>
+      </c>
+      <c r="F134" t="n">
+        <v>1.19984</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.59527</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.5852200000000001</v>
+      </c>
+      <c r="I134" t="n">
+        <v>1.14851</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.57694</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.86493</v>
+      </c>
+      <c r="L134" t="n">
+        <v>1.47683</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.99619</v>
+      </c>
+      <c r="N134" t="n">
+        <v>1.01916</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.8510800000000001</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.80783</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.72422</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.74205</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.5210199999999999</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.5178200000000001</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.5267999999999999</v>
+      </c>
+      <c r="V134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.88737</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.77271</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.5206799999999999</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.5267999999999999</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.98377</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.9700299999999999</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.54035</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.77091</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.5222100000000001</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.5159900000000001</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.54034</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.536</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.95386</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.5321399999999999</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.5603899999999999</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.78872</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.5475599999999999</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35167</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.61252</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.48161</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.76314</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.77803</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.8694400000000001</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.58265</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.5894299999999999</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.28639</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>-0.02663</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.3736</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.363</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.6641699999999999</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.37518</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.64197</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.41203</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.86812</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>1.1211</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.56102</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>-0.02879</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>-0.03645</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.39121</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32379</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.55249</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.46398</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.4386</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.44987</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.7265</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.7192000000000001</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.8081</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.5515399999999999</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>1.02582</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>1.1882</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.6003999999999999</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.57831</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>1.19963</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.5688799999999999</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.84753</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>1.26799</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>1.32138</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>1.31943</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>1.13623</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.80183</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>1.14464</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.5391</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>1.05411</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.52111</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.83569</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.52258</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>1.0022</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>1.45669</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.5350199999999999</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>1.3876</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>1.49504</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>1.44271</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>1.19467</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>1.09516</v>
+      </c>
+      <c r="C135" t="n">
+        <v>1.54804</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1.28319</v>
+      </c>
+      <c r="E135" t="n">
+        <v>1.14758</v>
+      </c>
+      <c r="F135" t="n">
+        <v>1.27648</v>
+      </c>
+      <c r="G135" t="n">
+        <v>1.18628</v>
+      </c>
+      <c r="H135" t="n">
+        <v>1.24337</v>
+      </c>
+      <c r="I135" t="n">
+        <v>1.34388</v>
+      </c>
+      <c r="J135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.8738400000000001</v>
+      </c>
+      <c r="L135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N135" t="n">
+        <v>1.34172</v>
+      </c>
+      <c r="O135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P135" t="n">
+        <v>1.13738</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.5123</v>
+      </c>
+      <c r="R135" t="n">
+        <v>1.34291</v>
+      </c>
+      <c r="S135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T135" t="n">
+        <v>1.2776</v>
+      </c>
+      <c r="U135" t="n">
+        <v>1.30861</v>
+      </c>
+      <c r="V135" t="n">
+        <v>1.12141</v>
+      </c>
+      <c r="W135" t="n">
+        <v>1.29154</v>
+      </c>
+      <c r="X135" t="n">
+        <v>1.30896</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>1.32638</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>1.34381</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>1.41354</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>1.05426</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>1.22546</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.4734</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.51193</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.9731300000000001</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.74759</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.84834</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.6597000000000001</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23001</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.78276</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25797</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.2676</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.81568</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.42926</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.41281</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.27493</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.32893</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.25658</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>-0.03539</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>-0.01326</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.27668</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.35572</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.3737</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.21453</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.16831</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.61672</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.38531</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.58226</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.5944400000000001</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.7708200000000001</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.7750900000000001</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.60929</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.57866</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.6659400000000001</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.60772</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.51448</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.76464</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.62863</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.98414</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.7833600000000001</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.9178999999999999</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.9277000000000001</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.74105</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.47575</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>1.02563</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.79661</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.97762</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.8674299999999999</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>1.21594</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>1.24529</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>1.21265</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>1.00508</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.9857100000000001</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.88612</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.8217100000000001</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.96314</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>1.40981</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>1.44674</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.84776</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>1.3405</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.7319600000000001</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>1.34193</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.99094</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.82024</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.7928500000000001</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.67272</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.68077</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.67515</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.6948799999999999</v>
+      </c>
+      <c r="H136" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I136" t="n">
+        <v>1.07174</v>
+      </c>
+      <c r="J136" t="n">
+        <v>1.05672</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.58963</v>
+      </c>
+      <c r="L136" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.8847</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.7982</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.82516</v>
+      </c>
+      <c r="P136" t="n">
+        <v>1.79808</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R136" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S136" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T136" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U136" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V136" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.88697</v>
+      </c>
+      <c r="X136" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>1.03116</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.49705</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>1.41879</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.43674</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>1.51304</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.15317</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00092</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.15565</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02277</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03959</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01436</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04309</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04103</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04864</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.0483</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02445</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02947</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.03782</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04942</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00254</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.28018</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.0493</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03564</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01186</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.0353</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20777</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.27017</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28171</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.48706</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.44596</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.48376</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.57787</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.5157200000000001</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.50837</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.59376</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.52858</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.45882</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.66044</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.66557</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.7029099999999999</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.5119</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.50912</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.62637</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.6487200000000001</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.71878</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>1.181</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.59687</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.75634</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.6042000000000001</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.61997</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.63267</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.6588999999999999</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.60565</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.49802</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.80668</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E137" t="n">
+        <v>1.04424</v>
+      </c>
+      <c r="F137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G137" t="n">
+        <v>1.2356</v>
+      </c>
+      <c r="H137" t="n">
+        <v>1.22062</v>
+      </c>
+      <c r="I137" t="n">
+        <v>1.47301</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.9478</v>
+      </c>
+      <c r="K137" t="n">
+        <v>1.47003</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.5117</v>
+      </c>
+      <c r="M137" t="n">
+        <v>1.35461</v>
+      </c>
+      <c r="N137" t="n">
+        <v>1.38789</v>
+      </c>
+      <c r="O137" t="n">
+        <v>1.37265</v>
+      </c>
+      <c r="P137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>1.33856</v>
+      </c>
+      <c r="R137" t="n">
+        <v>1.26806</v>
+      </c>
+      <c r="S137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="W137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="X137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.60764</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>1.53772</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.8119400000000001</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.51676</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>1.33876</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>1.05292</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.87241</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.33203</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.57111</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.03444</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.15984</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>-0.04849000000000001</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-0.04957</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>-0.00307</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.04986</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.29889</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32427</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30609</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>-0.04302</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25441</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29183</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.38052</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32007</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.37091</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.48547</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.7231599999999999</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.7923</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.55375</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.65378</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.61678</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.7936799999999999</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.14081</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>1.00323</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>1.00149</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>1.0056</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>1.10205</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.59965</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.61037</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.53937</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.75513</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.75497</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>1.39228</v>
+      </c>
+      <c r="D138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.6604800000000001</v>
+      </c>
+      <c r="H138" t="n">
+        <v>1.5454</v>
+      </c>
+      <c r="I138" t="n">
+        <v>1.18456</v>
+      </c>
+      <c r="J138" t="n">
+        <v>1.24437</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.54826</v>
+      </c>
+      <c r="L138" t="n">
+        <v>1.13336</v>
+      </c>
+      <c r="M138" t="n">
+        <v>1.51864</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.85224</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.92335</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.88275</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>1.05086</v>
+      </c>
+      <c r="R138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S138" t="n">
+        <v>1.15848</v>
+      </c>
+      <c r="T138" t="n">
+        <v>1.36012</v>
+      </c>
+      <c r="U138" t="n">
+        <v>1.1347</v>
+      </c>
+      <c r="V138" t="n">
+        <v>1.32541</v>
+      </c>
+      <c r="W138" t="n">
+        <v>1.3391</v>
+      </c>
+      <c r="X138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>1.64007</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>1.45419</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>1.30252</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>1.5023</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>1.24235</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>1.32005</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.48851</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.8247599999999999</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.58497</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.27126</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.44523</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.05246</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.43476</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.30956</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.1067</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.24732</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.28371</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.29916</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.29119</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30968</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.2599</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31234</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30357</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30346</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32675</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.3192</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.47149</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31869</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.3257</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.3156</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.35679</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32275</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.44656</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.47294</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.36302</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.3729</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32445</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.46044</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.47923</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.46506</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.52626</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.4725</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.53931</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.36638</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.53583</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.5118199999999999</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.64976</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.66288</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.40502</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.62998</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.68072</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.59151</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>1.53656</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>1.06692</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>1.43499</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.8451900000000001</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>1.21894</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>1.19772</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.99705</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>1.72468</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.6936599999999999</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.7838999999999999</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.71846</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.77912</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.73952</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.8945299999999999</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.9843999999999999</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.88019</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.91789</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.82245</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.8069400000000001</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.7796900000000001</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.6518400000000001</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.71462</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.69309</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.69367</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.51646</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.64797</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.51201</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.69412</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.63318</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.62862</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.6356000000000001</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.62426</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.6193</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.61937</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.6637000000000001</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.62918</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.69284</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.6664099999999999</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.6935800000000001</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.62637</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.66508</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>1.28209</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.80149</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.73745</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.56513</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>1.48229</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.69248</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.5838</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.47594</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.46737</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.52496</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.554</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.52254</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.57501</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.48223</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.5102</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.34564</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.43402</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.30523</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.34795</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35378</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32531</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32265</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.31192</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33281</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32205</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.48218</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.44485</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.599</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.40285</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.40994</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.9834299999999999</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.74875</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.8211799999999999</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.37929</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.70986</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>1.72751</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.82882</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>1.28854</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>1.40643</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>1.43683</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.59239</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>1.0177</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>1.40056</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.7552300000000001</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.53867</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.5229199999999999</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>1.15106</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.81023</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.6151799999999999</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.79864</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.67532</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.5288200000000001</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.6737000000000001</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.65877</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.6627799999999999</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.50844</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.9238099999999999</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.75805</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.83026</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.7901</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.74553</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.6133500000000001</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.7229099999999999</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.53591</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.70616</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.70375</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.6955399999999999</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.64224</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.60825</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.6128899999999999</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.61387</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.61394</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.63927</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.47503</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.64975</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.63595</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.63397</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.6515599999999999</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.51114</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.7417</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.7442000000000001</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.92016</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.7820499999999999</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.5271</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.59389</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.5173</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.51819</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.60423</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.5466299999999999</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39062</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.53484</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35335</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37927</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.52842</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.51727</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.52127</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31039</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36358</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.37864</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.5847599999999999</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.5760299999999999</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.5354099999999999</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29265</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.33042</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.34958</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.32324</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.3164</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33683</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34371</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33334</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34127</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32478</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.3441</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.38261</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.6214299999999999</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.55163</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.53264</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.3696</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.5721900000000001</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.61146</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.5320199999999999</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.59117</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.5838</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.6665599999999999</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.45039</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>1.12893</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.93799</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.7535700000000001</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.76652</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.72451</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.9037500000000001</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.8860800000000001</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>1.6108</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.81926</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.604</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.80365</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.74485</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.00302</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>1.04137</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.85427</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.7419199999999999</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.63113</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.6304299999999999</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.63219</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.6592899999999999</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.43834</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.5898600000000001</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.5269400000000001</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.67808</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.51701</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.50697</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.69701</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.71269</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.69999</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.62152</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.5101600000000001</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.60611</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.90323</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.51012</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.49909</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.6752400000000001</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.64344</v>
+      </c>
+      <c r="S141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.6498400000000001</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.6660700000000001</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.50598</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.71368</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.50086</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.51462</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.81521</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.8251000000000001</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.5425</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.54398</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.52177</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.65632</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.6475</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.44545</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.58785</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.39587</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.45917</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.45857</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.36968</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.4067</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.3423</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.23747</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.30684</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.30132</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.20579</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.36124</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.34025</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.32402</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.18863</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.24435</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.03234</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.1629</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.27605</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.02739</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>-0.01817</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.16393</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.18687</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.03240999999999999</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.05079</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.30633</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.2719</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.23035</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.24801</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.32479</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34971</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.37773</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.33097</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.43312</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.44572</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.60956</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.52663</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.45784</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.44652</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.43032</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.53912</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.42006</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.51015</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.49333</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.75329</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.50944</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.60953</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.65118</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.5505399999999999</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.5585800000000001</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.51129</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.43585</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.46636</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.54401</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.52912</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.4287</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.6127100000000001</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.47711</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.46593</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.51488</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.48509</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.5167999999999999</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.5525599999999999</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.5626100000000001</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.6720700000000001</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.5739299999999999</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.47327</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.5294</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.48441</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.54155</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.4921</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.47936</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.46315</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.46778</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.46368</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.50151</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.47162</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.47189</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.46855</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.46435</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.46584</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.46259</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.46261</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.45329</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.45837</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.46143</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.45724</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.45048</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.4787</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.43809</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.41936</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.44623</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.45335</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.45882</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.45294</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.43281</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.3785</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.44409</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.35887</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.40203</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.34774</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.26432</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.30283</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.28371</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.34441</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.1418</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.30139</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.29369</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.2886</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.35222</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.29171</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.23396</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.10696</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.29246</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.27311</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.42423</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.27655</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32595</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.31209</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35283</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.33251</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32993</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.37423</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.39588</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.45804</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.45493</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.43624</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.44597</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.48371</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.4064</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.44463</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.44559</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.47641</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.4422</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.40379</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.53016</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.5816699999999999</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.4668</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.46808</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.45238</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.48495</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.53586</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.51916</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.47035</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.45536</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.42214</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.49281</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.5037</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.42562</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.44358</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.43906</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.43816</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.44322</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34871</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.5867</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.4596</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.61125</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37299</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.45148</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.4534</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.47343</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.48193</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.47272</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.47429</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.46056</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.44925</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.42946</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.50306</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.40779</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.4493</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.47756</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.46965</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.45853</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.45546</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.4401</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.44649</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.45017</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.45093</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.45211</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.43136</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.4383</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.3479100000000001</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.32023</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.3444</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17682</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30251</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.28921</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31324</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14645</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19967</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>-0.04894</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.23701</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>-0.04704</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>-0.04735</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.13364</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>-4e-05</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.03519</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.1769</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22787</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15778</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.24245</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.31044</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-0.0492</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.21944</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>-0.00154</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.202</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.15128</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.26423</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.2749</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32376</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.29125</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.31699</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.3491</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.36395</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.37696</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.47165</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.38523</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.41282</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.42063</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.40048</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.40176</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.3791</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.4777</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.57909</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.52832</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.49479</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.41313</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.46981</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.48832</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.48973</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.45762</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.48427</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.58516</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.40114</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.47518</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.49524</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.47134</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.39888</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.44906</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.4569</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.45026</v>
       </c>
     </row>
   </sheetData>
